--- a/product_upload/packages/67/file.xlsx
+++ b/product_upload/packages/67/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR7"/>
+  <dimension ref="A1:AT7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,185 +451,195 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Description / Ar*</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Description / En *</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Secondary package  manufacture</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Mapping Scientific Code</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Generic Code</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scientific - SMID</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Trade - SMID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Consumer Type</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Drug Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sub-Type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scientific Name</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Name / Ar</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Strength Unit</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Pharmaceutical Form</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Administration Route</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>AtcCode1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>AtcCode2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Size Unit</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Package Types</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Package Size</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Legal Status</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Product Control</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Distribute area</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Storage Conditions / Ar</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Marketing Company</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Marketing Country</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Manufacture Name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Main Agent</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Second Agent</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Third agent</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Authorization Status</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Last Update</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>level 1</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>level 2</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>level 3</t>
         </is>
@@ -661,69 +671,63 @@
           <t>3739184666-824-377373269313</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VILDAGLIPTIN,METFORMIN HYDROCHLORIDE</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Vtreat Met</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>50,1000</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Film-coated tablet</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -731,79 +735,85 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>60</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>do not store above 30°c</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 مئوية ) </t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Spectro Pharma</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>PHARMATHEN INTERNATIONAL</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>AL-TAIF PHARMACEUTICALS COMPANY (SPECTRO PHARMA)</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>0</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO2" t="n">
+      <c r="AQ2" t="n">
         <v>0</v>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>Baby Accessories</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Strollers</t>
         </is>
@@ -835,69 +845,63 @@
           <t>0673352725-070-991309766588</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>MIRTAZAPINE</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Razapena</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Film-coated tablet</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -905,79 +909,85 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>30</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>do not store above 30°c</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 مئوية ) </t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>0</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO3" t="n">
+      <c r="AQ3" t="n">
         <v>0</v>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>Baby Accessories</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Baby Carrier &amp; Carrycots</t>
         </is>
@@ -1009,69 +1019,63 @@
           <t>5249019919-722-004261642661</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>MIRTAZAPINE</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Razapena</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Film-coated tablet</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1079,84 +1083,90 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>30</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>do not store above 30°c</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 مئوية ) </t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>0</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>0</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO4" t="n">
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>Nutrition</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Sport Nutrition</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Creatine</t>
         </is>
@@ -1188,69 +1198,63 @@
           <t>6518632272-339-717742089022</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ONDANSETRON</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>VOMETRON</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Orodispersible film</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1258,74 +1262,80 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Sachet</t>
         </is>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>10</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>do not store above 30°c</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 مئوية ) </t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>Alrazi Pharmaceutical Industries Factory Co</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>Shilpa Medicare Ltd</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>AL RAZI PHARMA INDUSTRIES</t>
         </is>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>0</v>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO5" t="n">
+      <c r="AQ5" t="n">
         <v>0</v>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>Baby Beds / Sleeping</t>
         </is>
@@ -1357,69 +1367,63 @@
           <t>0722289028-174-492415587817</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>APIXABAN</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Experta</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Film-coated tablet</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1427,84 +1431,90 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>60</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>store below 30°c</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 درجة مئوية ) </t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
         </is>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>0</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>0</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO6" t="n">
+      <c r="AQ6" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>Nutrition</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Healthy Nutrition</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>Honey</t>
         </is>
@@ -1536,69 +1546,63 @@
           <t>2977505497-701-061985446217</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>APIXABAN</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Experta</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Film-coated tablet</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Oral use</t>
         </is>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1606,84 +1610,90 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Blister</t>
         </is>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>60</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Prescription</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Uncontrolled</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t xml:space="preserve">Pharmacy </t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>store below 30°c</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t xml:space="preserve">يحفظ في درجة حرارة الغرفة ( بحيث لا تتجاوز 30 درجة مئوية ) </t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
         </is>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>0</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>0</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="AO7" t="n">
+      <c r="AQ7" t="n">
         <v>0</v>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>Nutrition</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Healthy Nutrition</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>Hydration Drinks</t>
         </is>
@@ -1700,7 +1710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1736,100 +1746,110 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Description / Ar*</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Description / En *</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Vendor item code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -1866,92 +1886,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Thalia Clay Stick Mask Charcool 30 Gr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Thalia Clay Stick Mask Charcool 30 Gr detailed description.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>SKU-72343</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>154.68</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -1988,92 +2018,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Thalia Clay Stick Mask Calmpink 30 Gr</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Thalia Clay Stick Mask Calmpink 30 Gr detailed description.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>SKU-94497</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>387.51</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2110,92 +2150,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Thalia Clay Stick Mask Seaya 30 Gr</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Thalia Clay Stick Mask Seaya 30 Gr detailed description.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>SKU-86642</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>77.92</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2232,92 +2282,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicled Neck &amp; Chin Mask</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unicskin Unicled Neck &amp; Chin Mask detailed description.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>SKU-80305</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>197.56</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2354,92 +2414,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unictech Eye Mask</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unicskin Unictech Eye Mask detailed description.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>SKU-45565</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>209.61</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2476,92 +2546,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicled 5.0 Centurion Korean Mask</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unicskin Unicled 5.0 Centurion Korean Mask detailed description.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>SKU-68711</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>124.8</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2598,92 +2678,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicretinol++ Invisible Night Mask</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unicskin Unicretinol++ Invisible Night Mask detailed description.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>SKU-48482</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>228.71</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2720,92 +2810,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Uniccollagen Eye Flash Mask 10x2 Patchs</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unicskin Uniccollagen Eye Flash Mask 10x2 Patchs detailed description.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>SKU-56958</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>176.75</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2842,92 +2942,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Uniccollagen Volume Lip Mask 5x1 Patchs</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unicskin Uniccollagen Volume Lip Mask 5x1 Patchs detailed description.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>SKU-49436</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>295.76</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2964,92 +3074,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicrevive-X Mask</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unicskin Unicrevive-X Mask detailed description.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>SKU-52307</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>212.92</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3086,92 +3206,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Freestyle Libre 3 Reader</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Freestyle Libre 3 Reader detailed description.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>SKU-42897</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>78.81</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>12345678905</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3188,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3234,55 +3364,60 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Description / Ar*</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Period After Opening</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Ingredients (INCI) *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Size *</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Period After Opening</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
@@ -3329,51 +3464,56 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Uniceyes Triple Action Contour 15ml Airless</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>172.2</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3420,51 +3560,56 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unica+ Cream 50ml Airless</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>175.42</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3511,51 +3656,56 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unica+ 72h Hydro+ Cream 50ml Airless</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>146.59</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3602,51 +3752,56 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicwhite X-Treme Complex Cream 50ml Airless</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>255.68</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3693,51 +3848,56 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicdetox&amp;Go Cleanser Foam 100ml</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Cleansers</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>100</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>337.2</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3784,51 +3944,56 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicsun+ Dark Spot Control Cream 30ml</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>100</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>385.59</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3875,51 +4040,56 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicsun+ Dark Spot Control Perfect Bronze 30ml</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>100</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>158.19</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -3966,51 +4136,56 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicbody D-Pigment Xtreme Cream 100ml</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Skin Brightening</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>232.7</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4057,51 +4232,56 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicbody Slim Action X4 250ml</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>19.64</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4148,51 +4328,56 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unicmagic Shot 10x2ml Ampoules</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>100</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>72.48</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4239,51 +4424,56 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Unicskin Unic30-Day Skin Miracle Shot 30 Ampoules 1,5ml</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>478.35</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4330,51 +4520,56 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ La Roche-Posay Anthelios Uv Air Spf50+ 50ml</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Sun Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>494.37</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4421,51 +4616,56 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Burberry Her (W) Set Edp 50 Ml + Body Lotion 75 Ml</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>122.58</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4512,51 +4712,56 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Burberry Hero (M) Set Edt 100 Ml +10 Ml+Body Wash 75 Ml</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>100</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>490.43</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4603,51 +4808,56 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Burberry Hero (M) Set Edt 100 Ml +10 Ml + Shower Gel 75 Ml</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>100</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>120.12</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4694,51 +4904,56 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Giorgio Armani Si Passione (W) Gift Set Edp 100 Ml</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>100</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>404.26</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4785,51 +5000,56 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Giorgio Armani Armani Code Pour Homme Gift Set Edt 50 Ml</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>100</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>100.25</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4876,51 +5096,56 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Giorgio Armani Stronger With You Intensely Gift Set Edp100ml</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Cosmetics &amp; Beauty</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Gift Sets</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>100</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>433.97</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -4967,51 +5192,56 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Clara Sleek Set</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Skin Care</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Moisturizers</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>100</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>436.14</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
@@ -5058,51 +5288,56 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>وصف تفصيلي لـ Nutshell Hand Wash Dara&amp;apos;S Ice Cream 375 Ml</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Bath &amp; Personal Care</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Bath &amp; Body</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Hand Wash</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>100</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>125.37</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>

--- a/product_upload/packages/67/file.xlsx
+++ b/product_upload/packages/67/file.xlsx
@@ -599,49 +599,54 @@
           <t>Manufacture Name</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Main Agent</t>
+        </is>
+      </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Main Agent</t>
+          <t>Second Agent</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Second Agent</t>
+          <t>Third agent</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Third agent</t>
+          <t>Authorization Status</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>Authorization Status</t>
+          <t>Last Update</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>Last Update</t>
+          <t>price</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>level 1</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>level 1</t>
+          <t>level 2</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>level 2</t>
+          <t>level 3</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>level 3</t>
+          <t>Seller SKU</t>
         </is>
       </c>
     </row>
@@ -651,6 +656,7 @@
           <t>H0000036976</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>H0000036976</t>
@@ -671,6 +677,8 @@
           <t>3739184666-824-377373269313</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -684,6 +692,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Human</t>
@@ -789,33 +799,40 @@
           <t>PHARMATHEN INTERNATIONAL</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>AL-TAIF PHARMACEUTICALS COMPANY (SPECTRO PHARMA)</t>
         </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Baby Accessories</t>
+        </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Baby Accessories</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
           <t>Strollers</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>SKU-D3833758ED04</t>
         </is>
       </c>
     </row>
@@ -825,6 +842,7 @@
           <t>2907257887</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>2907257887</t>
@@ -845,6 +863,8 @@
           <t>0673352725-070-991309766588</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -858,6 +878,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Human</t>
@@ -963,33 +985,40 @@
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
         <v>0</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Baby Accessories</t>
+        </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Baby Accessories</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
           <t>Baby Carrier &amp; Carrycots</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>SKU-020B5424323B</t>
         </is>
       </c>
     </row>
@@ -999,6 +1028,7 @@
           <t>2907257888</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2907257888</t>
@@ -1019,6 +1049,8 @@
           <t>5249019919-722-004261642661</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1032,6 +1064,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Human</t>
@@ -1137,38 +1171,44 @@
           <t>SPIMACO</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>SPIMACO</t>
         </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Sport Nutrition</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Sport Nutrition</t>
+          <t>Creatine</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>Creatine</t>
+          <t>SKU-97FC70ADC5C5</t>
         </is>
       </c>
     </row>
@@ -1178,6 +1218,7 @@
           <t>2807257862</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2807257862</t>
@@ -1198,6 +1239,8 @@
           <t>6518632272-339-717742089022</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1211,6 +1254,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Human</t>
@@ -1316,28 +1361,36 @@
           <t>Shilpa Medicare Ltd</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>AL RAZI PHARMA INDUSTRIES</t>
         </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>Baby Beds / Sleeping</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>SKU-34831EE247D1</t>
         </is>
       </c>
     </row>
@@ -1347,6 +1400,7 @@
           <t>2907257889</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2907257889</t>
@@ -1367,6 +1421,8 @@
           <t>0722289028-174-492415587817</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1380,6 +1436,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Human</t>
@@ -1485,38 +1543,44 @@
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
         </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
         <v>0</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Healthy Nutrition</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Healthy Nutrition</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>SKU-8835F1B43FDE</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1590,7 @@
           <t>2907257890</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>2907257890</t>
@@ -1546,6 +1611,8 @@
           <t>2977505497-701-061985446217</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1559,6 +1626,8 @@
           <t>-</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Human</t>
@@ -1664,38 +1733,44 @@
           <t>Saudi Pharmaceutical Industries &amp; Medical Appliances Corporation</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>SAUDI PHARMACEUTICAL INDUSTRIES</t>
         </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Healthy Nutrition</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Healthy Nutrition</t>
+          <t>Hydration Drinks</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>Hydration Drinks</t>
+          <t>SKU-7C7FE4AA6716</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,7 +1831,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Vendor item code</t>
+          <t>Seller SKU</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1794,62 +1869,62 @@
           <t>Brand</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Model / Catalogue Number</t>
+        </is>
+      </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Model / Catalogue Number</t>
+          <t>Single Use</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Single Use</t>
+          <t>Legal Manufacturer</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Legal Manufacturer</t>
+          <t>UDI-DI</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>GMDN Code / Term</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>UDI-DI</t>
+          <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>GMDN Code / Term</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>SFDA Authorized Representative License No.</t>
+          <t>Power Source</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Warranty</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Power Source</t>
+          <t>Storage Conditions / En</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Warranty</t>
+          <t>Usage Instructions</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
-        <is>
-          <t>Storage Conditions / En</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Usage Instructions</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -1932,56 +2007,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="T2" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>100</v>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB2" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2064,56 +2139,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="T3" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>100</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB3" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2196,56 +2271,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="T4" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>100</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB4" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2328,56 +2403,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="T5" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>100</v>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB5" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2460,56 +2535,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="T6" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>100</v>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB6" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2592,56 +2667,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="T7" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>100</v>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB7" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2724,56 +2799,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="T8" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>100</v>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA8" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB8" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2856,56 +2931,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="T9" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>100</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA9" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB9" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2988,56 +3063,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="T10" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>100</v>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA10" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB10" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3120,56 +3195,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="T11" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>100</v>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA11" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB11" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3252,56 +3327,56 @@
           <t>Yusur Brand</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>MD-100</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>MD-100</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="T12" t="n">
         <v>12345678905</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SFDA123456</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>100</v>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>SFDA123456</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="AA12" t="n">
-        <v>12</v>
+          <t>Store below 25C</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>https://example.com/instructions.pdf</t>
+        </is>
       </c>
       <c r="AB12" t="inlineStr">
-        <is>
-          <t>Store below 25C</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>https://example.com/instructions.pdf</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3318,7 +3393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3382,44 +3457,49 @@
           <t>Level 3*</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Period After Opening</t>
+        </is>
+      </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Period After Opening</t>
+          <t>Ingredients (INCI) *</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Size *</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Manufacturer *</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Ingredients (INCI) *</t>
+          <t>price</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Size *</t>
+          <t>Period After Opening.1</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Manufacturer *</t>
+          <t>Usage Instructions</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Warnings</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Period After Opening</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Usage Instructions</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Warnings</t>
+          <t>Seller SKU</t>
         </is>
       </c>
     </row>
@@ -3482,40 +3562,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>100</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SKU-0EA541E6A9B8</t>
         </is>
       </c>
     </row>
@@ -3578,40 +3663,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>175.42</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>100</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>175.42</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SKU-32D5B744278B</t>
         </is>
       </c>
     </row>
@@ -3674,40 +3764,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>146.59</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>100</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>146.59</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SKU-E258203AD54E</t>
         </is>
       </c>
     </row>
@@ -3770,40 +3865,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>255.68</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>100</v>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>255.68</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SKU-CFAB54E74D89</t>
         </is>
       </c>
     </row>
@@ -3866,40 +3966,45 @@
           <t>Cleansers</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>100</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>337.2</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SKU-7D187EA30596</t>
         </is>
       </c>
     </row>
@@ -3962,40 +4067,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>100</v>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>385.59</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SKU-86A60E7CF348</t>
         </is>
       </c>
     </row>
@@ -4058,40 +4168,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>158.19</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>100</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>158.19</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SKU-469D96FFC962</t>
         </is>
       </c>
     </row>
@@ -4154,40 +4269,45 @@
           <t>Skin Brightening</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>232.7</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>100</v>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>232.7</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SKU-DC85067CD61D</t>
         </is>
       </c>
     </row>
@@ -4250,40 +4370,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>100</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SKU-24ACCCB4226F</t>
         </is>
       </c>
     </row>
@@ -4346,40 +4471,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>100</v>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SKU-D01695E3CD03</t>
         </is>
       </c>
     </row>
@@ -4442,40 +4572,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>100</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478.35</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>100</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>478.35</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SKU-2FECD9A2C528</t>
         </is>
       </c>
     </row>
@@ -4538,40 +4673,45 @@
           <t>Sun Care</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>100</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>494.37</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>100</v>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>494.37</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SKU-7439B33B9DE4</t>
         </is>
       </c>
     </row>
@@ -4634,40 +4774,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>100</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>122.58</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>100</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>122.58</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SKU-744AEF206672</t>
         </is>
       </c>
     </row>
@@ -4730,40 +4875,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490.43</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>100</v>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>490.43</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SKU-B359C693F089</t>
         </is>
       </c>
     </row>
@@ -4826,40 +4976,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>100</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>120.12</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>100</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>120.12</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SKU-71E66890A830</t>
         </is>
       </c>
     </row>
@@ -4922,40 +5077,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>100</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>404.26</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>100</v>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>404.26</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SKU-40074E187278</t>
         </is>
       </c>
     </row>
@@ -5018,40 +5178,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>100</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>100</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SKU-957850B8F25E</t>
         </is>
       </c>
     </row>
@@ -5114,40 +5279,45 @@
           <t>Gift Sets</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>100</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>433.97</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>100</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>433.97</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SKU-E7CDD3C02D27</t>
         </is>
       </c>
     </row>
@@ -5210,40 +5380,45 @@
           <t>Moisturizers</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>100</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>436.14</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>100</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>436.14</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SKU-319E5C1223EE</t>
         </is>
       </c>
     </row>
@@ -5306,40 +5481,45 @@
           <t>Hand Wash</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>12M</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>125.37</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Aqua, Glycerin</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>100</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Yusur Pharma</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>125.37</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>12M</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SKU-5D507DF3425C</t>
         </is>
       </c>
     </row>

--- a/product_upload/packages/67/file.xlsx
+++ b/product_upload/packages/67/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Vtreat Met</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-D3833758ED04</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Razapena</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-020B5424323B</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1208,6 +1223,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Razapena</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-97FC70ADC5C5</t>
         </is>
       </c>
@@ -1231,7 +1251,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1390,6 +1410,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>VOMETRON</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-34831EE247D1</t>
         </is>
       </c>
@@ -1413,7 +1438,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1580,6 +1605,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Experta</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-8835F1B43FDE</t>
         </is>
       </c>
@@ -1603,7 +1633,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1769,6 +1799,11 @@
         </is>
       </c>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>Experta</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-7C7FE4AA6716</t>
         </is>
@@ -1785,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1831,100 +1866,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -1956,7 +1996,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1971,92 +2011,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-72343</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>154.68</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>685</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2088,7 +2133,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2103,92 +2148,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-94497</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>387.51</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>686</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2220,7 +2270,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2235,92 +2285,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-86642</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>77.92</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>687</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2352,7 +2407,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2367,92 +2422,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-80305</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>197.56</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>688</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2484,7 +2544,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2499,92 +2559,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-45565</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>209.61</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>689</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2616,7 +2681,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2631,92 +2696,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-68711</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>124.8</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>690</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2748,7 +2818,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2763,92 +2833,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-48482</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>228.71</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>691</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -2880,7 +2955,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2895,92 +2970,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-56958</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>176.75</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>692</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3012,7 +3092,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3027,92 +3107,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-49436</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>295.76</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>693</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3144,7 +3229,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3159,92 +3244,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-52307</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>212.92</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>694</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3276,7 +3366,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3291,92 +3381,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-42897</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>78.81</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>695</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -3393,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3499,6 +3594,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -3534,7 +3639,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3599,6 +3704,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-0EA541E6A9B8</t>
         </is>
@@ -3635,7 +3750,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3700,6 +3815,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-32D5B744278B</t>
         </is>
@@ -3736,7 +3861,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3801,6 +3926,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-E258203AD54E</t>
         </is>
@@ -3837,7 +3972,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3902,6 +4037,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-CFAB54E74D89</t>
         </is>
@@ -3938,7 +4083,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4003,6 +4148,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-7D187EA30596</t>
         </is>
@@ -4039,7 +4194,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4104,6 +4259,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-86A60E7CF348</t>
         </is>
@@ -4140,7 +4305,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4205,6 +4370,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-469D96FFC962</t>
         </is>
@@ -4241,7 +4416,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4306,6 +4481,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-DC85067CD61D</t>
         </is>
@@ -4342,7 +4527,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4407,6 +4592,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-24ACCCB4226F</t>
         </is>
@@ -4443,7 +4638,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4508,6 +4703,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-D01695E3CD03</t>
         </is>
@@ -4544,7 +4749,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4609,6 +4814,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-2FECD9A2C528</t>
         </is>
@@ -4645,7 +4860,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4710,6 +4925,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-7439B33B9DE4</t>
         </is>
@@ -4746,7 +4971,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4811,6 +5036,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-744AEF206672</t>
         </is>
@@ -4847,7 +5082,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4912,6 +5147,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-B359C693F089</t>
         </is>
@@ -4948,7 +5193,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5013,6 +5258,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-71E66890A830</t>
         </is>
@@ -5049,7 +5304,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5114,6 +5369,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-40074E187278</t>
         </is>
@@ -5150,7 +5415,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5215,6 +5480,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-957850B8F25E</t>
         </is>
@@ -5251,7 +5526,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5316,6 +5591,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-E7CDD3C02D27</t>
         </is>
@@ -5352,7 +5637,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5417,6 +5702,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-319E5C1223EE</t>
         </is>
@@ -5453,7 +5748,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5518,6 +5813,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-5D507DF3425C</t>
         </is>
